--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="564" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFBE4B5F-B25A-4788-809D-71AC7F63741A}"/>
+  <xr:revisionPtr revIDLastSave="578" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE736CFD-1D57-4B6C-80C4-C6BBEF6139E0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -419,12 +419,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,6 +521,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -908,72 +912,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12624479</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1107,7 +1111,7 @@
       <c r="M7" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="21" t="s">
+      <c r="N7" s="18" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1153,7 +1157,7 @@
       <c r="M8" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="21" t="s">
+      <c r="N8" s="18" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1199,7 +1203,7 @@
       <c r="M9" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="21" t="s">
+      <c r="N9" s="18" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1245,7 +1249,7 @@
       <c r="M10" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="21" t="s">
+      <c r="N10" s="18" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1291,7 +1295,7 @@
       <c r="M11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="21" t="s">
+      <c r="N11" s="18" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1337,7 +1341,7 @@
       <c r="M12" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="21" t="s">
+      <c r="N12" s="18" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1383,7 +1387,7 @@
       <c r="M13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="N13" s="21" t="s">
+      <c r="N13" s="18" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1429,7 +1433,7 @@
       <c r="M14" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N14" s="21" t="s">
+      <c r="N14" s="18" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2767,27 +2771,51 @@
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+    <row r="44" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B44" s="14">
+        <v>420</v>
+      </c>
+      <c r="C44" s="14">
+        <v>20</v>
+      </c>
+      <c r="D44" s="14">
+        <v>120</v>
+      </c>
+      <c r="E44" s="14">
+        <v>30</v>
+      </c>
+      <c r="F44" s="14">
+        <v>250</v>
+      </c>
+      <c r="G44" s="14">
+        <v>4</v>
+      </c>
+      <c r="H44" s="14">
+        <v>60</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DIVITA\OneDrive\Documents\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="578" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE736CFD-1D57-4B6C-80C4-C6BBEF6139E0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>2026-0913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Had a very chill Sunday with plenty of rest and some free time. Did a little studying </t>
   </si>
 </sst>
 </file>
@@ -523,10 +526,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -897,7 +896,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N405"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1049,11 +1048,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I73" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J73" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1071,7 +1070,7 @@
     </row>
     <row r="7" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B7" s="14">
         <v>420</v>
@@ -1095,7 +1094,7 @@
         <v>30</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="0"/>
+        <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>960</v>
       </c>
       <c r="J7" s="15">
@@ -1115,9 +1114,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="B8" s="14">
         <v>420</v>
@@ -1126,458 +1125,450 @@
         <v>20</v>
       </c>
       <c r="D8" s="14">
+        <v>60</v>
+      </c>
+      <c r="E8" s="14">
+        <v>30</v>
+      </c>
+      <c r="F8" s="14">
+        <v>400</v>
+      </c>
+      <c r="G8" s="14">
+        <v>7</v>
+      </c>
+      <c r="H8" s="14">
+        <v>30</v>
+      </c>
+      <c r="I8" s="15">
+        <v>960</v>
+      </c>
+      <c r="J8" s="15">
+        <v>480</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" s="18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>180</v>
+      </c>
+      <c r="E9" s="14">
+        <v>120</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
+      <c r="I9" s="15">
+        <v>870</v>
+      </c>
+      <c r="J9" s="15">
+        <v>570</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>180</v>
+      </c>
+      <c r="E10" s="14">
+        <v>120</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>60</v>
+      </c>
+      <c r="I10" s="15">
+        <v>870</v>
+      </c>
+      <c r="J10" s="15">
+        <v>570</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>20</v>
+      </c>
+      <c r="D11" s="14">
+        <v>60</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
+        <v>400</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>30</v>
+      </c>
+      <c r="I11" s="15">
+        <v>960</v>
+      </c>
+      <c r="J11" s="15">
+        <v>480</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11" s="18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420</v>
+      </c>
+      <c r="C12" s="14">
+        <v>20</v>
+      </c>
+      <c r="D12" s="14">
         <v>90</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E12" s="14">
         <v>60</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F12" s="14">
         <v>300</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G12" s="14">
         <v>5</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H12" s="14">
         <v>60</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
         <v>950</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
         <v>490</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K12" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L12" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="M12" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="18" t="s">
+      <c r="N12" s="18" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
+    <row r="13" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
         <v>46253</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B13" s="14">
         <v>420</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C13" s="14">
         <v>20</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D13" s="14">
         <v>120</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E13" s="14">
         <v>60</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F13" s="14">
         <v>250</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G13" s="14">
         <v>4</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H13" s="14">
         <v>60</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
         <v>930</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
         <v>510</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K13" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="L13" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M13" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="18" t="s">
+      <c r="N13" s="18" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="13">
+    <row r="14" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
         <v>46254</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B14" s="14">
         <v>420</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C14" s="14">
         <v>20</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D14" s="14">
         <v>90</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E14" s="14">
         <v>60</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F14" s="14">
         <v>300</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G14" s="14">
         <v>6</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H14" s="14">
         <v>60</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
         <v>950</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
         <v>490</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K14" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="L14" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="M14" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="18" t="s">
+      <c r="N14" s="18" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="13">
+    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
         <v>46255</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B15" s="14">
         <v>420</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C15" s="14">
         <v>20</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D15" s="14">
         <v>60</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E15" s="14">
         <v>30</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F15" s="14">
         <v>400</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G15" s="14">
         <v>7</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H15" s="14">
         <v>30</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
         <v>960</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K15" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="L15" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M15" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="18" t="s">
+      <c r="N15" s="18" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="13">
+    <row r="16" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
         <v>46256</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B16" s="14">
         <v>480</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C16" s="14">
         <v>30</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D16" s="14">
         <v>180</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E16" s="14">
         <v>120</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F16" s="14">
         <v>0</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G16" s="14">
         <v>0</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H16" s="14">
         <v>60</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
         <v>870</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
         <v>570</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K16" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="L16" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="M16" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="18" t="s">
+      <c r="N16" s="18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
+    <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
         <v>46257</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B17" s="14">
         <v>480</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C17" s="14">
         <v>30</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D17" s="14">
         <v>180</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E17" s="14">
         <v>120</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F17" s="14">
         <v>0</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G17" s="14">
         <v>0</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H17" s="14">
         <v>60</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
         <v>870</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
         <v>570</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K17" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="L17" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M13" s="16" t="s">
+      <c r="M17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="N13" s="18" t="s">
+      <c r="N17" s="18" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="13">
-        <v>46258</v>
-      </c>
-      <c r="B14" s="14">
-        <v>420</v>
-      </c>
-      <c r="C14" s="14">
-        <v>20</v>
-      </c>
-      <c r="D14" s="14">
-        <v>60</v>
-      </c>
-      <c r="E14" s="14">
-        <v>30</v>
-      </c>
-      <c r="F14" s="14">
-        <v>400</v>
-      </c>
-      <c r="G14" s="14">
-        <v>5</v>
-      </c>
-      <c r="H14" s="14">
-        <v>30</v>
-      </c>
-      <c r="I14" s="15">
-        <f t="shared" si="0"/>
-        <v>960</v>
-      </c>
-      <c r="J14" s="15">
-        <f t="shared" si="1"/>
-        <v>480</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="N14" s="18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="13">
-        <v>46259</v>
-      </c>
-      <c r="B15" s="14">
-        <v>420</v>
-      </c>
-      <c r="C15" s="14">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
-        <v>90</v>
-      </c>
-      <c r="E15" s="14">
-        <v>60</v>
-      </c>
-      <c r="F15" s="14">
-        <v>300</v>
-      </c>
-      <c r="G15" s="14">
-        <v>5</v>
-      </c>
-      <c r="H15" s="14">
-        <v>60</v>
-      </c>
-      <c r="I15" s="15">
-        <f t="shared" si="0"/>
-        <v>950</v>
-      </c>
-      <c r="J15" s="15">
-        <f t="shared" si="1"/>
-        <v>490</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="13">
-        <v>46260</v>
-      </c>
-      <c r="B16" s="14">
-        <v>420</v>
-      </c>
-      <c r="C16" s="14">
-        <v>20</v>
-      </c>
-      <c r="D16" s="14">
-        <v>120</v>
-      </c>
-      <c r="E16" s="14">
-        <v>60</v>
-      </c>
-      <c r="F16" s="14">
-        <v>250</v>
-      </c>
-      <c r="G16" s="14">
-        <v>4</v>
-      </c>
-      <c r="H16" s="14">
-        <v>60</v>
-      </c>
-      <c r="I16" s="15">
-        <f t="shared" si="0"/>
-        <v>930</v>
-      </c>
-      <c r="J16" s="15">
-        <f t="shared" si="1"/>
-        <v>510</v>
-      </c>
-      <c r="K16" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L16" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="13">
-        <v>46261</v>
-      </c>
-      <c r="B17" s="14">
-        <v>420</v>
-      </c>
-      <c r="C17" s="14">
-        <v>20</v>
-      </c>
-      <c r="D17" s="14">
-        <v>90</v>
-      </c>
-      <c r="E17" s="14">
-        <v>60</v>
-      </c>
-      <c r="F17" s="14">
-        <v>300</v>
-      </c>
-      <c r="G17" s="14">
-        <v>6</v>
-      </c>
-      <c r="H17" s="14">
-        <v>60</v>
-      </c>
-      <c r="I17" s="15">
-        <f t="shared" si="0"/>
-        <v>950</v>
-      </c>
-      <c r="J17" s="15">
-        <f t="shared" si="1"/>
-        <v>490</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>46262</v>
+        <v>46258</v>
       </c>
       <c r="B18" s="14">
         <v>420</v>
@@ -1595,7 +1586,7 @@
         <v>400</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H18" s="14">
         <v>30</v>
@@ -1609,50 +1600,50 @@
         <v>480</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N18" s="17" t="s">
-        <v>61</v>
+      <c r="N18" s="18" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
-        <v>46263</v>
+        <v>46259</v>
       </c>
       <c r="B19" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C19" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D19" s="14">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E19" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F19" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G19" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H19" s="14">
         <v>60</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>950</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>490</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>49</v>
@@ -1664,58 +1655,58 @@
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>46264</v>
+        <v>46260</v>
       </c>
       <c r="B20" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C20" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E20" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F20" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G20" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
         <v>60</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>930</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>510</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="L20" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="B21" s="14">
         <v>420</v>
@@ -1724,44 +1715,44 @@
         <v>20</v>
       </c>
       <c r="D21" s="14">
+        <v>90</v>
+      </c>
+      <c r="E21" s="14">
         <v>60</v>
       </c>
-      <c r="E21" s="14">
-        <v>30</v>
-      </c>
       <c r="F21" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G21" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="B22" s="14">
         <v>420</v>
@@ -1770,73 +1761,73 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E22" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F22" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H22" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>46267</v>
+        <v>46263</v>
       </c>
       <c r="B23" s="14">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C23" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D23" s="14">
+        <v>180</v>
+      </c>
+      <c r="E23" s="14">
         <v>120</v>
       </c>
-      <c r="E23" s="14">
-        <v>60</v>
-      </c>
       <c r="F23" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H23" s="14">
         <v>60</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>870</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>570</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>49</v>
@@ -1848,58 +1839,58 @@
         <v>51</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
-        <v>46268</v>
+        <v>46264</v>
       </c>
       <c r="B24" s="14">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E24" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F24" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G24" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H24" s="14">
         <v>60</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>870</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>570</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="B25" s="14">
         <v>420</v>
@@ -1917,7 +1908,7 @@
         <v>400</v>
       </c>
       <c r="G25" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H25" s="14">
         <v>30</v>
@@ -1931,50 +1922,50 @@
         <v>480</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
-        <v>46270</v>
+        <v>46266</v>
       </c>
       <c r="B26" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C26" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D26" s="14">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E26" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F26" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G26" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H26" s="14">
         <v>60</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>950</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>490</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>49</v>
@@ -1986,58 +1977,58 @@
         <v>51</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
-        <v>46271</v>
+        <v>46267</v>
       </c>
       <c r="B27" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C27" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E27" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F27" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G27" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
         <v>60</v>
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>930</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>510</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="L27" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="B28" s="14">
         <v>420</v>
@@ -2046,44 +2037,44 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
+        <v>90</v>
+      </c>
+      <c r="E28" s="14">
         <v>60</v>
       </c>
-      <c r="E28" s="14">
-        <v>30</v>
-      </c>
       <c r="F28" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="B29" s="14">
         <v>420</v>
@@ -2092,73 +2083,73 @@
         <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E29" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F29" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G29" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H29" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
-        <v>46274</v>
+        <v>46270</v>
       </c>
       <c r="B30" s="14">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C30" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D30" s="14">
+        <v>180</v>
+      </c>
+      <c r="E30" s="14">
         <v>120</v>
       </c>
-      <c r="E30" s="14">
-        <v>60</v>
-      </c>
       <c r="F30" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H30" s="14">
         <v>60</v>
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>870</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>570</v>
       </c>
       <c r="K30" s="16" t="s">
         <v>49</v>
@@ -2170,58 +2161,58 @@
         <v>51</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
-        <v>46275</v>
+        <v>46271</v>
       </c>
       <c r="B31" s="14">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C31" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D31" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E31" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F31" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G31" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H31" s="14">
         <v>60</v>
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>870</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>570</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="13">
-        <v>46276</v>
+        <v>46272</v>
       </c>
       <c r="B32" s="14">
         <v>420</v>
@@ -2239,7 +2230,7 @@
         <v>400</v>
       </c>
       <c r="G32" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H32" s="14">
         <v>30</v>
@@ -2253,50 +2244,50 @@
         <v>480</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M32" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A33" s="13">
-        <v>46277</v>
+        <v>46273</v>
       </c>
       <c r="B33" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C33" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D33" s="14">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E33" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F33" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G33" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H33" s="14">
         <v>60</v>
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>950</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>490</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>49</v>
@@ -2308,58 +2299,58 @@
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="13" t="s">
-        <v>67</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46274</v>
       </c>
       <c r="B34" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C34" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D34" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E34" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F34" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G34" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H34" s="14">
         <v>60</v>
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>930</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>510</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="L34" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A35" s="13">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="B35" s="14">
         <v>420</v>
@@ -2368,44 +2359,44 @@
         <v>20</v>
       </c>
       <c r="D35" s="14">
+        <v>90</v>
+      </c>
+      <c r="E35" s="14">
         <v>60</v>
       </c>
-      <c r="E35" s="14">
-        <v>30</v>
-      </c>
       <c r="F35" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G35" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H35" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="13">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="B36" s="14">
         <v>420</v>
@@ -2414,73 +2405,73 @@
         <v>20</v>
       </c>
       <c r="D36" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E36" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F36" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G36" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H36" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="13">
-        <v>46281</v>
+        <v>46277</v>
       </c>
       <c r="B37" s="14">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C37" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D37" s="14">
+        <v>180</v>
+      </c>
+      <c r="E37" s="14">
         <v>120</v>
       </c>
-      <c r="E37" s="14">
-        <v>60</v>
-      </c>
       <c r="F37" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G37" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H37" s="14">
         <v>60</v>
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>870</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>570</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>49</v>
@@ -2492,58 +2483,58 @@
         <v>51</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="13">
-        <v>46282</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="B38" s="14">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C38" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D38" s="14">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E38" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F38" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G38" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H38" s="14">
         <v>60</v>
       </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>870</v>
       </c>
       <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>570</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="13">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="B39" s="14">
         <v>420</v>
@@ -2561,7 +2552,7 @@
         <v>400</v>
       </c>
       <c r="G39" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H39" s="14">
         <v>30</v>
@@ -2575,50 +2566,50 @@
         <v>480</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M39" s="16" t="s">
         <v>56</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="13">
-        <v>46284</v>
+        <v>46280</v>
       </c>
       <c r="B40" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C40" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D40" s="14">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E40" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F40" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G40" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H40" s="14">
         <v>60</v>
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>950</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>490</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>49</v>
@@ -2630,58 +2621,58 @@
         <v>51</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" s="13">
-        <v>46285</v>
+        <v>46281</v>
       </c>
       <c r="B41" s="14">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="C41" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D41" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E41" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F41" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G41" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H41" s="14">
         <v>60</v>
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>930</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>510</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="L41" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="13">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B42" s="14">
         <v>420</v>
@@ -2690,44 +2681,44 @@
         <v>20</v>
       </c>
       <c r="D42" s="14">
+        <v>90</v>
+      </c>
+      <c r="E42" s="14">
         <v>60</v>
       </c>
-      <c r="E42" s="14">
-        <v>30</v>
-      </c>
       <c r="F42" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G42" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H42" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="13">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="B43" s="14">
         <v>420</v>
@@ -2742,67 +2733,67 @@
         <v>30</v>
       </c>
       <c r="F43" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G43" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H43" s="14">
         <v>30</v>
       </c>
       <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v>860</v>
+        <v>960</v>
       </c>
       <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>480</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L43" s="16" t="s">
         <v>59</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A44" s="13">
-        <v>46288</v>
+        <v>46284</v>
       </c>
       <c r="B44" s="14">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="C44" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D44" s="14">
+        <v>180</v>
+      </c>
+      <c r="E44" s="14">
         <v>120</v>
       </c>
-      <c r="E44" s="14">
-        <v>30</v>
-      </c>
       <c r="F44" s="14">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G44" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H44" s="14">
         <v>60</v>
       </c>
       <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>870</v>
       </c>
       <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>570</v>
       </c>
       <c r="K44" s="16" t="s">
         <v>49</v>
@@ -2814,140 +2805,284 @@
         <v>51</v>
       </c>
       <c r="N44" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B45" s="14">
+        <v>480</v>
+      </c>
+      <c r="C45" s="14">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14">
+        <v>180</v>
+      </c>
+      <c r="E45" s="14">
+        <v>120</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>60</v>
+      </c>
+      <c r="I45" s="15">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J45" s="15">
+        <f t="shared" si="1"/>
+        <v>570</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B46" s="14">
+        <v>420</v>
+      </c>
+      <c r="C46" s="14">
+        <v>20</v>
+      </c>
+      <c r="D46" s="14">
+        <v>60</v>
+      </c>
+      <c r="E46" s="14">
+        <v>30</v>
+      </c>
+      <c r="F46" s="14">
+        <v>400</v>
+      </c>
+      <c r="G46" s="14">
+        <v>5</v>
+      </c>
+      <c r="H46" s="14">
+        <v>30</v>
+      </c>
+      <c r="I46" s="15">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J46" s="15">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B47" s="14">
+        <v>420</v>
+      </c>
+      <c r="C47" s="14">
+        <v>20</v>
+      </c>
+      <c r="D47" s="14">
+        <v>60</v>
+      </c>
+      <c r="E47" s="14">
+        <v>30</v>
+      </c>
+      <c r="F47" s="14">
+        <v>300</v>
+      </c>
+      <c r="G47" s="14">
+        <v>5</v>
+      </c>
+      <c r="H47" s="14">
+        <v>30</v>
+      </c>
+      <c r="I47" s="15">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J47" s="15">
+        <f t="shared" si="1"/>
+        <v>580</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+    <row r="48" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B48" s="14">
+        <v>420</v>
+      </c>
+      <c r="C48" s="14">
+        <v>20</v>
+      </c>
+      <c r="D48" s="14">
+        <v>120</v>
+      </c>
+      <c r="E48" s="14">
+        <v>30</v>
+      </c>
+      <c r="F48" s="14">
+        <v>250</v>
+      </c>
+      <c r="G48" s="14">
+        <v>4</v>
+      </c>
+      <c r="H48" s="14">
+        <v>60</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B49" s="14">
+        <v>420</v>
+      </c>
+      <c r="C49" s="14">
+        <v>20</v>
+      </c>
+      <c r="D49" s="14">
+        <v>90</v>
+      </c>
+      <c r="E49" s="14">
+        <v>60</v>
+      </c>
+      <c r="F49" s="14">
+        <v>300</v>
+      </c>
+      <c r="G49" s="14">
+        <v>6</v>
+      </c>
+      <c r="H49" s="14">
+        <v>60</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B50" s="14">
+        <v>420</v>
+      </c>
+      <c r="C50" s="14">
+        <v>20</v>
+      </c>
+      <c r="D50" s="14">
+        <v>60</v>
+      </c>
+      <c r="E50" s="14">
+        <v>30</v>
+      </c>
+      <c r="F50" s="14">
+        <v>400</v>
+      </c>
+      <c r="G50" s="14">
+        <v>7</v>
+      </c>
+      <c r="H50" s="14">
+        <v>30</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
@@ -3377,11 +3512,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3399,11 +3534,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3421,11 +3556,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3443,11 +3578,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3465,11 +3600,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I74:I137" si="2">IF(SUM(B74:F74,H74)=0,"",SUM(B74:F74,H74))</f>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J74:J137" si="3">IF(I74="","",1440-I74)</f>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -4785,11 +4920,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4807,11 +4942,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4829,11 +4964,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4851,11 +4986,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4873,11 +5008,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I138:I201" si="4">IF(SUM(B138:F138,H138)=0,"",SUM(B138:F138,H138))</f>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J138:J201" si="5">IF(I138="","",1440-I138)</f>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -6193,11 +6328,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6215,11 +6350,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6237,11 +6372,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6259,11 +6394,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6281,11 +6416,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I202:I265" si="6">IF(SUM(B202:F202,H202)=0,"",SUM(B202:F202,H202))</f>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J202:J265" si="7">IF(I202="","",1440-I202)</f>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -7601,11 +7736,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7623,11 +7758,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7645,11 +7780,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7667,11 +7802,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7689,11 +7824,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I266:I329" si="8">IF(SUM(B266:F266,H266)=0,"",SUM(B266:F266,H266))</f>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J266:J329" si="9">IF(I266="","",1440-I266)</f>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -9009,11 +9144,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9031,11 +9166,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9053,11 +9188,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9075,11 +9210,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9097,11 +9232,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I330:I393" si="10">IF(SUM(B330:F330,H330)=0,"",SUM(B330:F330,H330))</f>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J330:J393" si="11">IF(I330="","",1440-I330)</f>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -10417,11 +10552,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10439,11 +10574,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10461,11 +10596,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10483,11 +10618,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10505,11 +10640,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I394:I405" si="12">IF(SUM(B394:F394,H394)=0,"",SUM(B394:F394,H394))</f>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J394:J405" si="13">IF(I394="","",1440-I394)</f>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10671,6 +10806,94 @@
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
     </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A402" s="13"/>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J402" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K402" s="16"/>
+      <c r="L402" s="16"/>
+      <c r="M402" s="16"/>
+      <c r="N402" s="17"/>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A403" s="13"/>
+      <c r="B403" s="14"/>
+      <c r="C403" s="14"/>
+      <c r="D403" s="14"/>
+      <c r="E403" s="14"/>
+      <c r="F403" s="14"/>
+      <c r="G403" s="14"/>
+      <c r="H403" s="14"/>
+      <c r="I403" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J403" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K403" s="16"/>
+      <c r="L403" s="16"/>
+      <c r="M403" s="16"/>
+      <c r="N403" s="17"/>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A404" s="13"/>
+      <c r="B404" s="14"/>
+      <c r="C404" s="14"/>
+      <c r="D404" s="14"/>
+      <c r="E404" s="14"/>
+      <c r="F404" s="14"/>
+      <c r="G404" s="14"/>
+      <c r="H404" s="14"/>
+      <c r="I404" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J404" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K404" s="16"/>
+      <c r="L404" s="16"/>
+      <c r="M404" s="16"/>
+      <c r="N404" s="17"/>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A405" s="13"/>
+      <c r="B405" s="14"/>
+      <c r="C405" s="14"/>
+      <c r="D405" s="14"/>
+      <c r="E405" s="14"/>
+      <c r="F405" s="14"/>
+      <c r="G405" s="14"/>
+      <c r="H405" s="14"/>
+      <c r="I405" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J405" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K405" s="16"/>
+      <c r="L405" s="16"/>
+      <c r="M405" s="16"/>
+      <c r="N405" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10680,21 +10903,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J405">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K405" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L405" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M405" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DIVITA\OneDrive\Documents\CAP776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{433B51EF-A2DB-488D-BEF4-AA0683599833}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -237,9 +237,6 @@
   <si>
     <t xml:space="preserve">Spent the day attending classes and working on study and coding. Felt a little tired but had a good day overall.
 </t>
-  </si>
-  <si>
-    <t>2026-0913</t>
   </si>
   <si>
     <t xml:space="preserve">Had a very chill Sunday with plenty of rest and some free time. Did a little studying </t>
@@ -1243,7 +1240,7 @@
         <v>64</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2487,8 +2484,8 @@
       </c>
     </row>
     <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="s">
-        <v>67</v>
+      <c r="A38" s="13">
+        <v>46278</v>
       </c>
       <c r="B38" s="14">
         <v>480</v>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{433B51EF-A2DB-488D-BEF4-AA0683599833}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFB17300-72DE-49D5-9CB3-8C16A041E495}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -240,6 +240,15 @@
   </si>
   <si>
     <t xml:space="preserve">Had a very chill Sunday with plenty of rest and some free time. Did a little studying </t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Had a stressful day today. Did  a little studying as well.</t>
   </si>
 </sst>
 </file>
@@ -523,6 +532,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3081,49 +3094,97 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+    <row r="51" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B51" s="14">
+        <v>480</v>
+      </c>
+      <c r="C51" s="14">
+        <v>20</v>
+      </c>
+      <c r="D51" s="14">
+        <v>90</v>
+      </c>
+      <c r="E51" s="14">
+        <v>60</v>
+      </c>
+      <c r="F51" s="14">
+        <v>50</v>
+      </c>
+      <c r="G51" s="14">
+        <v>1</v>
+      </c>
+      <c r="H51" s="14">
+        <v>60</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B52" s="14">
+        <v>420</v>
+      </c>
+      <c r="C52" s="14">
+        <v>0</v>
+      </c>
+      <c r="D52" s="14">
+        <v>90</v>
+      </c>
+      <c r="E52" s="14">
+        <v>30</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>60</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>840</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af60c3abce6b75c0/Documents/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFB17300-72DE-49D5-9CB3-8C16A041E495}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="13_ncr:1_{AFBB6CB5-BEC5-42DE-98A4-A324BFA6F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86CD4BFF-F519-4860-A4E3-AF92DC467A14}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -249,6 +249,24 @@
   </si>
   <si>
     <t>Had a stressful day today. Did  a little studying as well.</t>
+  </si>
+  <si>
+    <t>Travelled back to my home</t>
+  </si>
+  <si>
+    <t>Travelling</t>
+  </si>
+  <si>
+    <t>Aug-Sep-Oct</t>
+  </si>
+  <si>
+    <t>Felt a little tired but had a good day overall.</t>
+  </si>
+  <si>
+    <t>Nothing much happened, but the day went fine.</t>
+  </si>
+  <si>
+    <t>Spent some time studying and also took time to chill.</t>
   </si>
 </sst>
 </file>
@@ -967,7 +985,9 @@
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21"/>
+      <c r="F3" s="21" t="s">
+        <v>73</v>
+      </c>
       <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -3099,7 +3119,7 @@
         <v>46291</v>
       </c>
       <c r="B51" s="14">
-        <v>480</v>
+        <v>350</v>
       </c>
       <c r="C51" s="14">
         <v>20</v>
@@ -3121,11 +3141,11 @@
       </c>
       <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v>760</v>
+        <v>630</v>
       </c>
       <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>810</v>
       </c>
       <c r="K51" s="16" t="s">
         <v>59</v>
@@ -3145,16 +3165,16 @@
         <v>46292</v>
       </c>
       <c r="B52" s="14">
-        <v>420</v>
+        <v>120</v>
       </c>
       <c r="C52" s="14">
         <v>0</v>
       </c>
       <c r="D52" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E52" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F52" s="14">
         <v>0</v>
@@ -3163,15 +3183,15 @@
         <v>0</v>
       </c>
       <c r="H52" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>1290</v>
       </c>
       <c r="K52" s="16" t="s">
         <v>68</v>
@@ -3187,158 +3207,326 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B53" s="14">
+        <v>120</v>
+      </c>
+      <c r="C53" s="14">
+        <v>0</v>
+      </c>
+      <c r="D53" s="14">
+        <v>0</v>
+      </c>
+      <c r="E53" s="14">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>0</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>120</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>1320</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B54" s="14">
+        <v>300</v>
+      </c>
+      <c r="C54" s="14">
+        <v>0</v>
+      </c>
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>0</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>300</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B55" s="14">
+        <v>350</v>
+      </c>
+      <c r="C55" s="14">
+        <v>0</v>
+      </c>
+      <c r="D55" s="14">
+        <v>60</v>
+      </c>
+      <c r="E55" s="14">
+        <v>30</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>60</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>500</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B56" s="14">
+        <v>420</v>
+      </c>
+      <c r="C56" s="14">
+        <v>60</v>
+      </c>
+      <c r="D56" s="14">
+        <v>120</v>
+      </c>
+      <c r="E56" s="14">
+        <v>30</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>120</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B57" s="14">
+        <v>420</v>
+      </c>
+      <c r="C57" s="14">
+        <v>60</v>
+      </c>
+      <c r="D57" s="14">
+        <v>120</v>
+      </c>
+      <c r="E57" s="14">
+        <v>60</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>120</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B58" s="14">
+        <v>420</v>
+      </c>
+      <c r="C58" s="14">
+        <v>60</v>
+      </c>
+      <c r="D58" s="14">
+        <v>120</v>
+      </c>
+      <c r="E58" s="14">
+        <v>60</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>120</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A59" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B59" s="14">
+        <v>420</v>
+      </c>
+      <c r="C59" s="14">
+        <v>0</v>
+      </c>
+      <c r="D59" s="14">
+        <v>120</v>
+      </c>
+      <c r="E59" s="14">
+        <v>30</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>120</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
